--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-produit-de-sante.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-produit-de-sante.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$76</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2395" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="297">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -846,6 +846,10 @@
     <t>ED.thumbnail</t>
   </si>
   <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
+  </si>
+  <si>
     <t>ManufacturedProduct.manufacturedMaterial.code.qualifier</t>
   </si>
   <si>
@@ -905,6 +909,22 @@
   </si>
   <si>
     <t>Material.lotNumberText</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.sdtcExpirationTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVL-TS
+</t>
+  </si>
+  <si>
+    <t>The date and time the manufacturer no longer ensures the safety, quality, and/or proper functioning of the material.</t>
+  </si>
+  <si>
+    <t>There is a need in many situations that the materials used are of a specific quality or potency or functional status. The ending date for this guarantee is specified by the manufacturer. After that date, while the material may still provide the same characteristics, the manufacturer no longer takes responsibility that the product will perform as specified and denies responsibility for failure of the material after that date.</t>
+  </si>
+  <si>
+    <t>Material.sdtcExpirationTime</t>
   </si>
   <si>
     <t>ManufacturedProduct.manufacturerOrganization</t>
@@ -1228,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK75"/>
+  <dimension ref="A1:AK76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.62890625" customWidth="true" bestFit="true"/>
@@ -1245,7 +1265,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -8395,7 +8415,7 @@
         <v>74</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>74</v>
+        <v>270</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>74</v>
@@ -8403,17 +8423,17 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F71" t="s" s="2">
         <v>80</v>
@@ -8431,11 +8451,11 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8486,7 +8506,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8506,17 +8526,17 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>80</v>
@@ -8534,13 +8554,13 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8591,7 +8611,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8611,10 +8631,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8637,10 +8657,10 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -8692,7 +8712,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8712,10 +8732,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8738,10 +8758,10 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -8793,7 +8813,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8813,10 +8833,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8839,12 +8859,16 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
+      <c r="M75" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>74</v>
       </c>
@@ -8892,7 +8916,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -8910,8 +8934,107 @@
         <v>74</v>
       </c>
     </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK75">
+  <autoFilter ref="A1:AK76">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8921,7 +9044,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI75">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
